--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/GEORGIA_2023.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/GEORGIA_2023.xlsx
@@ -3210,7 +3210,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C159">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C189">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C315">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Huichapa</t>
+          <t>Huichapan</t>
         </is>
       </c>
       <c r="C449">
@@ -22722,7 +22722,7 @@
       </c>
       <c r="B1243" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1243">
